--- a/public/guides/product-template.xlsx
+++ b/public/guides/product-template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16259" uniqueCount="3620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16059" uniqueCount="3473">
   <si>
     <t>商品名称</t>
   </si>
@@ -10446,447 +10446,6 @@
   </si>
   <si>
     <t>6901028007733</t>
-  </si>
-  <si>
-    <t>白沙(硬长丰)</t>
-  </si>
-  <si>
-    <t>6901028249256</t>
-  </si>
-  <si>
-    <t>6901028249249</t>
-  </si>
-  <si>
-    <t>南洋双喜(硬龙凤)</t>
-  </si>
-  <si>
-    <t>南洋</t>
-  </si>
-  <si>
-    <t>4891132016610</t>
-  </si>
-  <si>
-    <t>4891132016603</t>
-  </si>
-  <si>
-    <t>555(硬金天越)</t>
-  </si>
-  <si>
-    <t>119.09</t>
-  </si>
-  <si>
-    <t>555</t>
-  </si>
-  <si>
-    <t>8888075056014</t>
-  </si>
-  <si>
-    <t>8888075056007</t>
-  </si>
-  <si>
-    <t>南洋红双喜(硬龙凤紫)</t>
-  </si>
-  <si>
-    <t>123.04</t>
-  </si>
-  <si>
-    <t>4891132670058</t>
-  </si>
-  <si>
-    <t>4891132670041</t>
-  </si>
-  <si>
-    <t>阿里山(硬天韵)</t>
-  </si>
-  <si>
-    <t>阿里山</t>
-  </si>
-  <si>
-    <t>4719579946195</t>
-  </si>
-  <si>
-    <t>4719579946188</t>
-  </si>
-  <si>
-    <t>555(硬金.锐)</t>
-  </si>
-  <si>
-    <t>8888075005524</t>
-  </si>
-  <si>
-    <t>8888075005517</t>
-  </si>
-  <si>
-    <t>长城(醇雅薄荷180支)</t>
-  </si>
-  <si>
-    <t>158.40</t>
-  </si>
-  <si>
-    <t>长城</t>
-  </si>
-  <si>
-    <t>6901028084925</t>
-  </si>
-  <si>
-    <t>6901028084918</t>
-  </si>
-  <si>
-    <t>南京(硬梦都)</t>
-  </si>
-  <si>
-    <t>6901028115148</t>
-  </si>
-  <si>
-    <t>6901028115155</t>
-  </si>
-  <si>
-    <t>爱喜(硬薄荷)</t>
-  </si>
-  <si>
-    <t>196.24</t>
-  </si>
-  <si>
-    <t>爱喜</t>
-  </si>
-  <si>
-    <t>8801116006458</t>
-  </si>
-  <si>
-    <t>8801116006441</t>
-  </si>
-  <si>
-    <t>牡丹(恒大硬中支)</t>
-  </si>
-  <si>
-    <t>6901028212700</t>
-  </si>
-  <si>
-    <t>6901028212694</t>
-  </si>
-  <si>
-    <t>万宝路(硬金3.0)</t>
-  </si>
-  <si>
-    <t>6901028064996</t>
-  </si>
-  <si>
-    <t>6901028064989</t>
-  </si>
-  <si>
-    <t>梅花王(硬里拉蓝超细支)</t>
-  </si>
-  <si>
-    <t>202.39</t>
-  </si>
-  <si>
-    <t>梅花王</t>
-  </si>
-  <si>
-    <t>4711588703493</t>
-  </si>
-  <si>
-    <t>4711588703400</t>
-  </si>
-  <si>
-    <t>爱喜(硬幻变)</t>
-  </si>
-  <si>
-    <t>207.97</t>
-  </si>
-  <si>
-    <t>8801116005581</t>
-  </si>
-  <si>
-    <t>8801116005574</t>
-  </si>
-  <si>
-    <t>宝亨宝珠(硬)</t>
-  </si>
-  <si>
-    <t>宝亨</t>
-  </si>
-  <si>
-    <t>8801116003914</t>
-  </si>
-  <si>
-    <t>8801116003907</t>
-  </si>
-  <si>
-    <t>南洋双喜(硬南洋1905)</t>
-  </si>
-  <si>
-    <t>211.38</t>
-  </si>
-  <si>
-    <t>4891132580029</t>
-  </si>
-  <si>
-    <t>4891132580012</t>
-  </si>
-  <si>
-    <t>555(硬老版细支)</t>
-  </si>
-  <si>
-    <t>212.28</t>
-  </si>
-  <si>
-    <t>8888075034777</t>
-  </si>
-  <si>
-    <t>8888075034760</t>
-  </si>
-  <si>
-    <t>555(硬冰炫)</t>
-  </si>
-  <si>
-    <t>216.05</t>
-  </si>
-  <si>
-    <t>8888075024037</t>
-  </si>
-  <si>
-    <t>8888075024020</t>
-  </si>
-  <si>
-    <t>大华(硬黄金眼)</t>
-  </si>
-  <si>
-    <t>217.74</t>
-  </si>
-  <si>
-    <t>大华</t>
-  </si>
-  <si>
-    <t>4719579941329</t>
-  </si>
-  <si>
-    <t>4719579941336</t>
-  </si>
-  <si>
-    <t>南洋双喜(罐装吉祥龙凤)</t>
-  </si>
-  <si>
-    <t>218.54</t>
-  </si>
-  <si>
-    <t>4891132441337</t>
-  </si>
-  <si>
-    <t>4891132441306</t>
-  </si>
-  <si>
-    <t>万宝路(硬冰爵2.0)</t>
-  </si>
-  <si>
-    <t>6901028204026</t>
-  </si>
-  <si>
-    <t>6901028204019</t>
-  </si>
-  <si>
-    <t>南洋双喜(硬爱国绿中支)</t>
-  </si>
-  <si>
-    <t>225.73</t>
-  </si>
-  <si>
-    <t>4891132601014</t>
-  </si>
-  <si>
-    <t>4891132601007</t>
-  </si>
-  <si>
-    <t>建牌(薄荷4)新</t>
-  </si>
-  <si>
-    <t>234.91</t>
-  </si>
-  <si>
-    <t>建牌</t>
-  </si>
-  <si>
-    <t>8888075074872</t>
-  </si>
-  <si>
-    <t>8888075074841</t>
-  </si>
-  <si>
-    <t>建牌(HD细支1)新</t>
-  </si>
-  <si>
-    <t>8888075054645</t>
-  </si>
-  <si>
-    <t>8888075054638</t>
-  </si>
-  <si>
-    <t>阿里山(硬景泰典蓝)</t>
-  </si>
-  <si>
-    <t>235.32</t>
-  </si>
-  <si>
-    <t>4719579946164</t>
-  </si>
-  <si>
-    <t>4719579946157</t>
-  </si>
-  <si>
-    <t>大华(硬开元)</t>
-  </si>
-  <si>
-    <t>245.00</t>
-  </si>
-  <si>
-    <t>4719579941008</t>
-  </si>
-  <si>
-    <t>4719579940995</t>
-  </si>
-  <si>
-    <t>爱喜(硬幻变倍享)</t>
-  </si>
-  <si>
-    <t>246.69</t>
-  </si>
-  <si>
-    <t>8801116037575</t>
-  </si>
-  <si>
-    <t>8801116037582</t>
-  </si>
-  <si>
-    <t>555(硬国际版)</t>
-  </si>
-  <si>
-    <t>254.92</t>
-  </si>
-  <si>
-    <t>8888075034715</t>
-  </si>
-  <si>
-    <t>8888075034708</t>
-  </si>
-  <si>
-    <t>建牌(薄荷黄冰)新</t>
-  </si>
-  <si>
-    <t>257.75</t>
-  </si>
-  <si>
-    <t>8888075074858</t>
-  </si>
-  <si>
-    <t>8888075074827</t>
-  </si>
-  <si>
-    <t>建牌(薄荷紫冰)新</t>
-  </si>
-  <si>
-    <t>8888075074865</t>
-  </si>
-  <si>
-    <t>8888075074834</t>
-  </si>
-  <si>
-    <t>555(硬双冰)</t>
-  </si>
-  <si>
-    <t>271.07</t>
-  </si>
-  <si>
-    <t>8888075018616</t>
-  </si>
-  <si>
-    <t>8888075018609</t>
-  </si>
-  <si>
-    <t>泰山(中海御叶双中支)</t>
-  </si>
-  <si>
-    <t>6901028158275</t>
-  </si>
-  <si>
-    <t>6901028158268</t>
-  </si>
-  <si>
-    <t>中华(软金短支新)</t>
-  </si>
-  <si>
-    <t>6901028212618</t>
-  </si>
-  <si>
-    <t>6901028212601</t>
-  </si>
-  <si>
-    <t>云烟(硬云端中支)</t>
-  </si>
-  <si>
-    <t>6901028333214</t>
-  </si>
-  <si>
-    <t>6901028333207</t>
-  </si>
-  <si>
-    <t>熊猫(硬经典细支)</t>
-  </si>
-  <si>
-    <t>6901028212670</t>
-  </si>
-  <si>
-    <t>6901028212663</t>
-  </si>
-  <si>
-    <t>6901028064842</t>
-  </si>
-  <si>
-    <t>6901028064835</t>
-  </si>
-  <si>
-    <t>双喜(硬红火好日子)</t>
-  </si>
-  <si>
-    <t>6901028057561</t>
-  </si>
-  <si>
-    <t>6901028057554</t>
-  </si>
-  <si>
-    <t>中华(硬细支6mg)</t>
-  </si>
-  <si>
-    <t>6901028212885</t>
-  </si>
-  <si>
-    <t>6901028212878</t>
-  </si>
-  <si>
-    <t>牡丹(硬蓝彩细支)</t>
-  </si>
-  <si>
-    <t>6901028212748</t>
-  </si>
-  <si>
-    <t>6901028212731</t>
-  </si>
-  <si>
-    <t>芙蓉王(硬品悦细支)</t>
-  </si>
-  <si>
-    <t>6901028278263</t>
-  </si>
-  <si>
-    <t>6901028278256</t>
-  </si>
-  <si>
-    <t>白沙(硬开心就好中支)</t>
-  </si>
-  <si>
-    <t>6901028278232</t>
-  </si>
-  <si>
-    <t>6901028278225</t>
   </si>
 </sst>
 </file>
@@ -10899,7 +10458,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10912,13 +10471,6 @@
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -11383,28 +10935,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -11413,118 +10968,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -11879,7 +11431,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T843"/>
+  <dimension ref="A1:T803"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -61665,686 +61217,6 @@
         <v>39</v>
       </c>
     </row>
-    <row r="804" spans="1:20">
-      <c r="A804" t="s">
-        <v>3473</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1396</v>
-      </c>
-      <c r="C804" t="s">
-        <v>424</v>
-      </c>
-      <c r="D804" t="s">
-        <v>3474</v>
-      </c>
-      <c r="E804" t="s">
-        <v>3475</v>
-      </c>
-    </row>
-    <row r="805" spans="1:20">
-      <c r="A805" t="s">
-        <v>3476</v>
-      </c>
-      <c r="B805" t="s">
-        <v>610</v>
-      </c>
-      <c r="C805" t="s">
-        <v>3477</v>
-      </c>
-      <c r="D805" t="s">
-        <v>3478</v>
-      </c>
-      <c r="E805" t="s">
-        <v>3479</v>
-      </c>
-    </row>
-    <row r="806" spans="1:20">
-      <c r="A806" t="s">
-        <v>3480</v>
-      </c>
-      <c r="B806" t="s">
-        <v>3481</v>
-      </c>
-      <c r="C806" t="s">
-        <v>3482</v>
-      </c>
-      <c r="D806" t="s">
-        <v>3483</v>
-      </c>
-      <c r="E806" t="s">
-        <v>3484</v>
-      </c>
-    </row>
-    <row r="807" spans="1:20">
-      <c r="A807" t="s">
-        <v>3485</v>
-      </c>
-      <c r="B807" t="s">
-        <v>3486</v>
-      </c>
-      <c r="C807" t="s">
-        <v>3477</v>
-      </c>
-      <c r="D807" t="s">
-        <v>3487</v>
-      </c>
-      <c r="E807" t="s">
-        <v>3488</v>
-      </c>
-    </row>
-    <row r="808" spans="1:20">
-      <c r="A808" t="s">
-        <v>3489</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1478</v>
-      </c>
-      <c r="C808" t="s">
-        <v>3490</v>
-      </c>
-      <c r="D808" t="s">
-        <v>3491</v>
-      </c>
-      <c r="E808" t="s">
-        <v>3492</v>
-      </c>
-    </row>
-    <row r="809" spans="1:20">
-      <c r="A809" t="s">
-        <v>3493</v>
-      </c>
-      <c r="B809" t="s">
-        <v>2617</v>
-      </c>
-      <c r="C809" t="s">
-        <v>3482</v>
-      </c>
-      <c r="D809" t="s">
-        <v>3494</v>
-      </c>
-      <c r="E809" t="s">
-        <v>3495</v>
-      </c>
-    </row>
-    <row r="810" spans="1:20">
-      <c r="A810" t="s">
-        <v>3496</v>
-      </c>
-      <c r="B810" t="s">
-        <v>3497</v>
-      </c>
-      <c r="C810" t="s">
-        <v>3498</v>
-      </c>
-      <c r="D810" t="s">
-        <v>3499</v>
-      </c>
-      <c r="E810" t="s">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="811" spans="1:20">
-      <c r="A811" t="s">
-        <v>3501</v>
-      </c>
-      <c r="B811" t="s">
-        <v>154</v>
-      </c>
-      <c r="C811" t="s">
-        <v>42</v>
-      </c>
-      <c r="D811" t="s">
-        <v>3502</v>
-      </c>
-      <c r="E811" t="s">
-        <v>3503</v>
-      </c>
-    </row>
-    <row r="812" spans="1:20">
-      <c r="A812" t="s">
-        <v>3504</v>
-      </c>
-      <c r="B812" t="s">
-        <v>3505</v>
-      </c>
-      <c r="C812" t="s">
-        <v>3506</v>
-      </c>
-      <c r="D812" t="s">
-        <v>3507</v>
-      </c>
-      <c r="E812" t="s">
-        <v>3508</v>
-      </c>
-    </row>
-    <row r="813" spans="1:20">
-      <c r="A813" t="s">
-        <v>3509</v>
-      </c>
-      <c r="B813" t="s">
-        <v>402</v>
-      </c>
-      <c r="C813" t="s">
-        <v>538</v>
-      </c>
-      <c r="D813" t="s">
-        <v>3510</v>
-      </c>
-      <c r="E813" t="s">
-        <v>3511</v>
-      </c>
-    </row>
-    <row r="814" spans="1:20">
-      <c r="A814" t="s">
-        <v>3512</v>
-      </c>
-      <c r="B814" t="s">
-        <v>402</v>
-      </c>
-      <c r="C814" t="s">
-        <v>626</v>
-      </c>
-      <c r="D814" t="s">
-        <v>3513</v>
-      </c>
-      <c r="E814" t="s">
-        <v>3514</v>
-      </c>
-    </row>
-    <row r="815" spans="1:20">
-      <c r="A815" t="s">
-        <v>3515</v>
-      </c>
-      <c r="B815" t="s">
-        <v>3516</v>
-      </c>
-      <c r="C815" t="s">
-        <v>3517</v>
-      </c>
-      <c r="D815" t="s">
-        <v>3518</v>
-      </c>
-      <c r="E815" t="s">
-        <v>3519</v>
-      </c>
-    </row>
-    <row r="816" spans="1:20">
-      <c r="A816" t="s">
-        <v>3520</v>
-      </c>
-      <c r="B816" t="s">
-        <v>3521</v>
-      </c>
-      <c r="C816" t="s">
-        <v>3506</v>
-      </c>
-      <c r="D816" t="s">
-        <v>3522</v>
-      </c>
-      <c r="E816" t="s">
-        <v>3523</v>
-      </c>
-    </row>
-    <row r="817" spans="1:5">
-      <c r="A817" t="s">
-        <v>3524</v>
-      </c>
-      <c r="B817" t="s">
-        <v>3521</v>
-      </c>
-      <c r="C817" t="s">
-        <v>3525</v>
-      </c>
-      <c r="D817" t="s">
-        <v>3526</v>
-      </c>
-      <c r="E817" t="s">
-        <v>3527</v>
-      </c>
-    </row>
-    <row r="818" spans="1:5">
-      <c r="A818" t="s">
-        <v>3528</v>
-      </c>
-      <c r="B818" t="s">
-        <v>3529</v>
-      </c>
-      <c r="C818" t="s">
-        <v>3477</v>
-      </c>
-      <c r="D818" t="s">
-        <v>3530</v>
-      </c>
-      <c r="E818" t="s">
-        <v>3531</v>
-      </c>
-    </row>
-    <row r="819" spans="1:5">
-      <c r="A819" t="s">
-        <v>3532</v>
-      </c>
-      <c r="B819" t="s">
-        <v>3533</v>
-      </c>
-      <c r="C819" t="s">
-        <v>3482</v>
-      </c>
-      <c r="D819" t="s">
-        <v>3534</v>
-      </c>
-      <c r="E819" t="s">
-        <v>3535</v>
-      </c>
-    </row>
-    <row r="820" spans="1:5">
-      <c r="A820" t="s">
-        <v>3536</v>
-      </c>
-      <c r="B820" t="s">
-        <v>3537</v>
-      </c>
-      <c r="C820" t="s">
-        <v>3482</v>
-      </c>
-      <c r="D820" t="s">
-        <v>3538</v>
-      </c>
-      <c r="E820" t="s">
-        <v>3539</v>
-      </c>
-    </row>
-    <row r="821" spans="1:5">
-      <c r="A821" t="s">
-        <v>3540</v>
-      </c>
-      <c r="B821" t="s">
-        <v>3541</v>
-      </c>
-      <c r="C821" t="s">
-        <v>3542</v>
-      </c>
-      <c r="D821" t="s">
-        <v>3543</v>
-      </c>
-      <c r="E821" t="s">
-        <v>3544</v>
-      </c>
-    </row>
-    <row r="822" spans="1:5">
-      <c r="A822" t="s">
-        <v>3545</v>
-      </c>
-      <c r="B822" t="s">
-        <v>3546</v>
-      </c>
-      <c r="C822" t="s">
-        <v>3477</v>
-      </c>
-      <c r="D822" t="s">
-        <v>3547</v>
-      </c>
-      <c r="E822" t="s">
-        <v>3548</v>
-      </c>
-    </row>
-    <row r="823" spans="1:5">
-      <c r="A823" t="s">
-        <v>3549</v>
-      </c>
-      <c r="B823" t="s">
-        <v>418</v>
-      </c>
-      <c r="C823" t="s">
-        <v>626</v>
-      </c>
-      <c r="D823" t="s">
-        <v>3550</v>
-      </c>
-      <c r="E823" t="s">
-        <v>3551</v>
-      </c>
-    </row>
-    <row r="824" spans="1:5">
-      <c r="A824" t="s">
-        <v>3552</v>
-      </c>
-      <c r="B824" t="s">
-        <v>3553</v>
-      </c>
-      <c r="C824" t="s">
-        <v>3477</v>
-      </c>
-      <c r="D824" t="s">
-        <v>3554</v>
-      </c>
-      <c r="E824" t="s">
-        <v>3555</v>
-      </c>
-    </row>
-    <row r="825" spans="1:5">
-      <c r="A825" t="s">
-        <v>3556</v>
-      </c>
-      <c r="B825" t="s">
-        <v>3557</v>
-      </c>
-      <c r="C825" t="s">
-        <v>3558</v>
-      </c>
-      <c r="D825" t="s">
-        <v>3559</v>
-      </c>
-      <c r="E825" t="s">
-        <v>3560</v>
-      </c>
-    </row>
-    <row r="826" spans="1:5">
-      <c r="A826" t="s">
-        <v>3561</v>
-      </c>
-      <c r="B826" t="s">
-        <v>3557</v>
-      </c>
-      <c r="C826" t="s">
-        <v>3558</v>
-      </c>
-      <c r="D826" t="s">
-        <v>3562</v>
-      </c>
-      <c r="E826" t="s">
-        <v>3563</v>
-      </c>
-    </row>
-    <row r="827" spans="1:5">
-      <c r="A827" t="s">
-        <v>3564</v>
-      </c>
-      <c r="B827" t="s">
-        <v>3565</v>
-      </c>
-      <c r="C827" t="s">
-        <v>3490</v>
-      </c>
-      <c r="D827" t="s">
-        <v>3566</v>
-      </c>
-      <c r="E827" t="s">
-        <v>3567</v>
-      </c>
-    </row>
-    <row r="828" spans="1:5">
-      <c r="A828" t="s">
-        <v>3568</v>
-      </c>
-      <c r="B828" t="s">
-        <v>3569</v>
-      </c>
-      <c r="C828" t="s">
-        <v>3542</v>
-      </c>
-      <c r="D828" t="s">
-        <v>3570</v>
-      </c>
-      <c r="E828" t="s">
-        <v>3571</v>
-      </c>
-    </row>
-    <row r="829" spans="1:5">
-      <c r="A829" t="s">
-        <v>3572</v>
-      </c>
-      <c r="B829" t="s">
-        <v>3573</v>
-      </c>
-      <c r="C829" t="s">
-        <v>3506</v>
-      </c>
-      <c r="D829" t="s">
-        <v>3574</v>
-      </c>
-      <c r="E829" t="s">
-        <v>3575</v>
-      </c>
-    </row>
-    <row r="830" spans="1:5">
-      <c r="A830" t="s">
-        <v>3576</v>
-      </c>
-      <c r="B830" t="s">
-        <v>3577</v>
-      </c>
-      <c r="C830" t="s">
-        <v>3482</v>
-      </c>
-      <c r="D830" t="s">
-        <v>3578</v>
-      </c>
-      <c r="E830" t="s">
-        <v>3579</v>
-      </c>
-    </row>
-    <row r="831" spans="1:5">
-      <c r="A831" t="s">
-        <v>3580</v>
-      </c>
-      <c r="B831" t="s">
-        <v>3581</v>
-      </c>
-      <c r="C831" t="s">
-        <v>3558</v>
-      </c>
-      <c r="D831" t="s">
-        <v>3582</v>
-      </c>
-      <c r="E831" t="s">
-        <v>3583</v>
-      </c>
-    </row>
-    <row r="832" spans="1:5">
-      <c r="A832" t="s">
-        <v>3584</v>
-      </c>
-      <c r="B832" t="s">
-        <v>3581</v>
-      </c>
-      <c r="C832" t="s">
-        <v>3558</v>
-      </c>
-      <c r="D832" t="s">
-        <v>3585</v>
-      </c>
-      <c r="E832" t="s">
-        <v>3586</v>
-      </c>
-    </row>
-    <row r="833" spans="1:5">
-      <c r="A833" t="s">
-        <v>3587</v>
-      </c>
-      <c r="B833" t="s">
-        <v>3588</v>
-      </c>
-      <c r="C833" t="s">
-        <v>3482</v>
-      </c>
-      <c r="D833" t="s">
-        <v>3589</v>
-      </c>
-      <c r="E833" t="s">
-        <v>3590</v>
-      </c>
-    </row>
-    <row r="834" spans="1:5">
-      <c r="A834" t="s">
-        <v>3591</v>
-      </c>
-      <c r="B834" t="s">
-        <v>664</v>
-      </c>
-      <c r="C834" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D834" t="s">
-        <v>3592</v>
-      </c>
-      <c r="E834" t="s">
-        <v>3593</v>
-      </c>
-    </row>
-    <row r="835" spans="1:5">
-      <c r="A835" t="s">
-        <v>3594</v>
-      </c>
-      <c r="B835" t="s">
-        <v>676</v>
-      </c>
-      <c r="C835" t="s">
-        <v>935</v>
-      </c>
-      <c r="D835" t="s">
-        <v>3595</v>
-      </c>
-      <c r="E835" t="s">
-        <v>3596</v>
-      </c>
-    </row>
-    <row r="836" spans="1:5">
-      <c r="A836" t="s">
-        <v>3597</v>
-      </c>
-      <c r="B836" t="s">
-        <v>139</v>
-      </c>
-      <c r="C836" t="s">
-        <v>207</v>
-      </c>
-      <c r="D836" t="s">
-        <v>3598</v>
-      </c>
-      <c r="E836" t="s">
-        <v>3599</v>
-      </c>
-    </row>
-    <row r="837" spans="1:5">
-      <c r="A837" t="s">
-        <v>3600</v>
-      </c>
-      <c r="B837" t="s">
-        <v>139</v>
-      </c>
-      <c r="C837" t="s">
-        <v>140</v>
-      </c>
-      <c r="D837" t="s">
-        <v>3601</v>
-      </c>
-      <c r="E837" t="s">
-        <v>3602</v>
-      </c>
-    </row>
-    <row r="838" spans="1:5">
-      <c r="A838" t="s">
-        <v>1279</v>
-      </c>
-      <c r="B838" t="s">
-        <v>77</v>
-      </c>
-      <c r="C838" t="s">
-        <v>424</v>
-      </c>
-      <c r="D838" t="s">
-        <v>3603</v>
-      </c>
-      <c r="E838" t="s">
-        <v>3604</v>
-      </c>
-    </row>
-    <row r="839" spans="1:5">
-      <c r="A839" t="s">
-        <v>3605</v>
-      </c>
-      <c r="B839" t="s">
-        <v>402</v>
-      </c>
-      <c r="C839" t="s">
-        <v>318</v>
-      </c>
-      <c r="D839" t="s">
-        <v>3606</v>
-      </c>
-      <c r="E839" t="s">
-        <v>3607</v>
-      </c>
-    </row>
-    <row r="840" spans="1:5">
-      <c r="A840" t="s">
-        <v>3608</v>
-      </c>
-      <c r="B840" t="s">
-        <v>2661</v>
-      </c>
-      <c r="C840" t="s">
-        <v>935</v>
-      </c>
-      <c r="D840" t="s">
-        <v>3609</v>
-      </c>
-      <c r="E840" t="s">
-        <v>3610</v>
-      </c>
-    </row>
-    <row r="841" spans="1:5">
-      <c r="A841" t="s">
-        <v>3611</v>
-      </c>
-      <c r="B841" t="s">
-        <v>312</v>
-      </c>
-      <c r="C841" t="s">
-        <v>538</v>
-      </c>
-      <c r="D841" t="s">
-        <v>3612</v>
-      </c>
-      <c r="E841" t="s">
-        <v>3613</v>
-      </c>
-    </row>
-    <row r="842" spans="1:5">
-      <c r="A842" t="s">
-        <v>3614</v>
-      </c>
-      <c r="B842" t="s">
-        <v>418</v>
-      </c>
-      <c r="C842" t="s">
-        <v>197</v>
-      </c>
-      <c r="D842" t="s">
-        <v>3615</v>
-      </c>
-      <c r="E842" t="s">
-        <v>3616</v>
-      </c>
-    </row>
-    <row r="843" spans="1:5">
-      <c r="A843" t="s">
-        <v>3617</v>
-      </c>
-      <c r="B843" t="s">
-        <v>154</v>
-      </c>
-      <c r="C843" t="s">
-        <v>424</v>
-      </c>
-      <c r="D843" t="s">
-        <v>3618</v>
-      </c>
-      <c r="E843" t="s">
-        <v>3619</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
